--- a/从零开始学Slots/从零开始学Slots-22-数值篇-不规则窗口(2).xlsx
+++ b/从零开始学Slots/从零开始学Slots-22-数值篇-不规则窗口(2).xlsx
@@ -9445,6 +9445,9 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:N215" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -11289,5 +11292,8 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:R115" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/从零开始学Slots/从零开始学Slots-22-数值篇-不规则窗口(2).xlsx
+++ b/从零开始学Slots/从零开始学Slots-22-数值篇-不规则窗口(2).xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="255">
   <si>
     <r>
       <rPr>
@@ -8122,7 +8122,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="39">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -8257,6 +8257,26 @@
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -9586,8 +9606,8 @@
       <c r="B11" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="C11" s="16" t="s">
-        <v>165</v>
+      <c r="C11" s="34">
+        <v>5</v>
       </c>
       <c r="D11" s="16"/>
       <c r="E11" s="16"/>
@@ -9631,40 +9651,40 @@
       <c r="A15" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B15" s="15" t="s">
-        <v>173</v>
-      </c>
-      <c r="C15" s="15" t="s">
-        <v>173</v>
-      </c>
-      <c r="D15" s="15" t="s">
-        <v>173</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>173</v>
-      </c>
-      <c r="F15" s="15" t="s">
-        <v>173</v>
+      <c r="B15" s="35">
+        <v>9</v>
+      </c>
+      <c r="C15" s="35">
+        <v>9</v>
+      </c>
+      <c r="D15" s="35">
+        <v>9</v>
+      </c>
+      <c r="E15" s="35">
+        <v>9</v>
+      </c>
+      <c r="F15" s="35">
+        <v>9</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B16" s="15" t="s">
-        <v>173</v>
-      </c>
-      <c r="C16" s="15" t="s">
-        <v>173</v>
-      </c>
-      <c r="D16" s="15" t="s">
-        <v>173</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>173</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>173</v>
+      <c r="B16" s="35">
+        <v>9</v>
+      </c>
+      <c r="C16" s="35">
+        <v>9</v>
+      </c>
+      <c r="D16" s="35">
+        <v>9</v>
+      </c>
+      <c r="E16" s="35">
+        <v>9</v>
+      </c>
+      <c r="F16" s="35">
+        <v>9</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9691,60 +9711,60 @@
       <c r="A18" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="B18" s="15" t="s">
-        <v>175</v>
-      </c>
-      <c r="C18" s="15" t="s">
-        <v>175</v>
-      </c>
-      <c r="D18" s="15" t="s">
-        <v>175</v>
-      </c>
-      <c r="E18" s="15" t="s">
-        <v>175</v>
-      </c>
-      <c r="F18" s="15" t="s">
-        <v>175</v>
+      <c r="B18" s="35">
+        <v>10</v>
+      </c>
+      <c r="C18" s="35">
+        <v>10</v>
+      </c>
+      <c r="D18" s="35">
+        <v>10</v>
+      </c>
+      <c r="E18" s="35">
+        <v>10</v>
+      </c>
+      <c r="F18" s="35">
+        <v>10</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="B19" s="15" t="s">
-        <v>175</v>
-      </c>
-      <c r="C19" s="15" t="s">
-        <v>175</v>
-      </c>
-      <c r="D19" s="15" t="s">
-        <v>175</v>
-      </c>
-      <c r="E19" s="15" t="s">
-        <v>175</v>
-      </c>
-      <c r="F19" s="15" t="s">
-        <v>175</v>
+      <c r="B19" s="35">
+        <v>10</v>
+      </c>
+      <c r="C19" s="35">
+        <v>10</v>
+      </c>
+      <c r="D19" s="35">
+        <v>10</v>
+      </c>
+      <c r="E19" s="35">
+        <v>10</v>
+      </c>
+      <c r="F19" s="35">
+        <v>10</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="B20" s="15" t="s">
-        <v>175</v>
-      </c>
-      <c r="C20" s="15" t="s">
-        <v>175</v>
-      </c>
-      <c r="D20" s="15" t="s">
-        <v>175</v>
-      </c>
-      <c r="E20" s="15" t="s">
-        <v>175</v>
-      </c>
-      <c r="F20" s="15" t="s">
-        <v>175</v>
+      <c r="B20" s="35">
+        <v>10</v>
+      </c>
+      <c r="C20" s="35">
+        <v>10</v>
+      </c>
+      <c r="D20" s="35">
+        <v>10</v>
+      </c>
+      <c r="E20" s="35">
+        <v>10</v>
+      </c>
+      <c r="F20" s="35">
+        <v>10</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10002,8 +10022,8 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="20" t="s">
-        <v>173</v>
+      <c r="A35" s="36">
+        <v>9</v>
       </c>
       <c r="B35" s="18" t="n">
         <f aca="false">COUNTIF(B15:B29,"9")+COUNTIF(B15:B29,"Wild")</f>
@@ -10034,8 +10054,8 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="20" t="s">
-        <v>175</v>
+      <c r="A36" s="36">
+        <v>10</v>
       </c>
       <c r="B36" s="18" t="n">
         <f aca="false">COUNTIF(B15:B29,"10")+COUNTIF(B15:B29,"Wild")</f>
@@ -10257,8 +10277,8 @@
       <c r="H44" s="14"/>
     </row>
     <row r="45" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="20" t="s">
-        <v>173</v>
+      <c r="A45" s="36">
+        <v>9</v>
       </c>
       <c r="B45" s="18" t="n">
         <f aca="false">B35*B30</f>
@@ -10286,8 +10306,8 @@
       <c r="H45" s="17"/>
     </row>
     <row r="46" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="20" t="s">
-        <v>175</v>
+      <c r="A46" s="36">
+        <v>10</v>
       </c>
       <c r="B46" s="18" t="n">
         <f aca="false">B36*B30</f>
@@ -10418,11 +10438,11 @@
         <v>192</v>
       </c>
       <c r="B52" s="14"/>
-      <c r="C52" s="21" t="s">
-        <v>173</v>
-      </c>
-      <c r="D52" s="21" t="s">
-        <v>175</v>
+      <c r="C52" s="37">
+        <v>9</v>
+      </c>
+      <c r="D52" s="37">
+        <v>10</v>
       </c>
       <c r="E52" s="21" t="s">
         <v>176</v>
@@ -10438,8 +10458,8 @@
       </c>
     </row>
     <row r="53" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="22" t="s">
-        <v>193</v>
+      <c r="A53" s="38">
+        <v>3</v>
       </c>
       <c r="C53" s="23" t="n">
         <v>75</v>
@@ -10465,8 +10485,8 @@
       <c r="M53" s="17"/>
     </row>
     <row r="54" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="22" t="s">
-        <v>195</v>
+      <c r="A54" s="38">
+        <v>4</v>
       </c>
       <c r="C54" s="23" t="n">
         <v>7</v>
@@ -10490,8 +10510,8 @@
       <c r="K54" s="17"/>
     </row>
     <row r="55" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="22" t="s">
-        <v>197</v>
+      <c r="A55" s="38">
+        <v>5</v>
       </c>
       <c r="C55" s="23" t="n">
         <v>1</v>
@@ -10553,8 +10573,8 @@
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="20" t="s">
-        <v>173</v>
+      <c r="A59" s="36">
+        <v>9</v>
       </c>
       <c r="B59" s="20" t="s">
         <v>205</v>
@@ -10583,8 +10603,8 @@
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="20" t="s">
-        <v>173</v>
+      <c r="A60" s="36">
+        <v>9</v>
       </c>
       <c r="B60" s="20" t="s">
         <v>206</v>
@@ -10613,8 +10633,8 @@
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="20" t="s">
-        <v>173</v>
+      <c r="A61" s="36">
+        <v>9</v>
       </c>
       <c r="B61" s="20" t="s">
         <v>207</v>
@@ -10643,8 +10663,8 @@
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="20" t="s">
-        <v>175</v>
+      <c r="A62" s="36">
+        <v>10</v>
       </c>
       <c r="B62" s="20" t="s">
         <v>208</v>
@@ -10673,8 +10693,8 @@
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="20" t="s">
-        <v>175</v>
+      <c r="A63" s="36">
+        <v>10</v>
       </c>
       <c r="B63" s="20" t="s">
         <v>209</v>
@@ -10703,8 +10723,8 @@
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="20" t="s">
-        <v>175</v>
+      <c r="A64" s="36">
+        <v>10</v>
       </c>
       <c r="B64" s="20" t="s">
         <v>210</v>
